--- a/CPS FY 25 26 to Fy 2627.xlsx
+++ b/CPS FY 25 26 to Fy 2627.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saten\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saten\Documents\kimi\workspace\CPS_OEM_Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C7927ADB-3E7C-4DA2-B273-EC574EC97B2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E32086E0-0062-4A90-9988-F439B75E23CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EDADC1A1-8BB4-4734-ABD4-05750D6A8A29}"/>
   </bookViews>

--- a/CPS FY 25 26 to Fy 2627.xlsx
+++ b/CPS FY 25 26 to Fy 2627.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saten\Documents\kimi\workspace\CPS_OEM_Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E32086E0-0062-4A90-9988-F439B75E23CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50AC2DD2-CDED-4BCF-8E28-ED4A181BF006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EDADC1A1-8BB4-4734-ABD4-05750D6A8A29}"/>
+    <workbookView xWindow="5760" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{EDADC1A1-8BB4-4734-ABD4-05750D6A8A29}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="19">
   <si>
     <t>Bajaj ( Incl. KTM &amp; TRM)</t>
   </si>
@@ -73,6 +73,24 @@
   </si>
   <si>
     <t>CM2 %</t>
+  </si>
+  <si>
+    <t>TVS:ICE Only</t>
+  </si>
+  <si>
+    <t>TVS:Bajaj+Chetak</t>
+  </si>
+  <si>
+    <t>Overall</t>
+  </si>
+  <si>
+    <t>FY Year</t>
+  </si>
+  <si>
+    <t>FY 25 26</t>
+  </si>
+  <si>
+    <t>FY 26 27</t>
   </si>
 </sst>
 </file>
@@ -601,7 +619,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DFAEAE1-3A10-4937-AB30-78999D6DDEA1}">
-  <dimension ref="C1:AI18"/>
+  <dimension ref="B1:AU18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -622,7 +640,7 @@
     <col min="19" max="19" width="7.6640625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="11.21875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.88671875" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="8.77734375" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="7.88671875" bestFit="1" customWidth="1"/>
@@ -635,10 +653,21 @@
     <col min="33" max="33" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="7.88671875" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="6.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:35" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="3:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:47" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:47" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D2" s="23" t="s">
         <v>0</v>
       </c>
@@ -687,8 +716,29 @@
       <c r="AG2" s="21"/>
       <c r="AH2" s="21"/>
       <c r="AI2" s="22"/>
+      <c r="AJ2" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK2" s="21"/>
+      <c r="AL2" s="21"/>
+      <c r="AM2" s="22"/>
+      <c r="AN2" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO2" s="21"/>
+      <c r="AP2" s="21"/>
+      <c r="AQ2" s="22"/>
+      <c r="AR2" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="AS2" s="21"/>
+      <c r="AT2" s="21"/>
+      <c r="AU2" s="22"/>
     </row>
-    <row r="3" spans="3:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:47" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
       <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
@@ -788,8 +838,47 @@
       <c r="AI3" s="4" t="s">
         <v>12</v>
       </c>
+      <c r="AJ3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AM3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="AN3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AO3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AQ3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="AR3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AS3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AT3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AU3" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="4" spans="3:35" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:47" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
       <c r="C4" s="5">
         <v>45748</v>
       </c>
@@ -873,8 +962,59 @@
       <c r="AI4" s="9">
         <v>0.88619999999999999</v>
       </c>
+      <c r="AJ4" s="6">
+        <f>T4-AF4</f>
+        <v>5593025</v>
+      </c>
+      <c r="AK4" s="7">
+        <f>U4-AG4</f>
+        <v>8165</v>
+      </c>
+      <c r="AL4" s="10">
+        <f>V4-AH4</f>
+        <v>1792418</v>
+      </c>
+      <c r="AM4" s="9">
+        <f>AL4/AJ4</f>
+        <v>0.3204738044260485</v>
+      </c>
+      <c r="AN4" s="6">
+        <f>D4+H4</f>
+        <v>1581000</v>
+      </c>
+      <c r="AO4" s="7">
+        <f t="shared" ref="AO4:AO18" si="0">E4+I4</f>
+        <v>1027</v>
+      </c>
+      <c r="AP4" s="10">
+        <f t="shared" ref="AP4:AP18" si="1">F4+J4</f>
+        <v>134616</v>
+      </c>
+      <c r="AQ4" s="9">
+        <f>AP4/AN4</f>
+        <v>8.5146110056926003E-2</v>
+      </c>
+      <c r="AR4" s="6">
+        <f>D4+H4+L4+P4+T4+X4+AB4</f>
+        <v>8608185</v>
+      </c>
+      <c r="AS4" s="7">
+        <f t="shared" ref="AS4:AS18" si="2">I4+M4</f>
+        <v>393</v>
+      </c>
+      <c r="AT4" s="10">
+        <f t="shared" ref="AT4:AT18" si="3">J4+N4</f>
+        <v>49914</v>
+      </c>
+      <c r="AU4" s="9">
+        <f>AT4/AR4</f>
+        <v>5.7984348617042963E-3</v>
+      </c>
     </row>
-    <row r="5" spans="3:35" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:47" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
       <c r="C5" s="5">
         <v>45778</v>
       </c>
@@ -958,8 +1098,59 @@
       <c r="AI5" s="14">
         <v>0.88280000000000003</v>
       </c>
+      <c r="AJ5" s="11">
+        <f t="shared" ref="AJ5:AJ18" si="4">T5-AF5</f>
+        <v>5271760</v>
+      </c>
+      <c r="AK5" s="12">
+        <f t="shared" ref="AK5:AK18" si="5">U5-AG5</f>
+        <v>7696</v>
+      </c>
+      <c r="AL5" s="15">
+        <f t="shared" ref="AL5:AL18" si="6">V5-AH5</f>
+        <v>524428</v>
+      </c>
+      <c r="AM5" s="14">
+        <f t="shared" ref="AM5:AM18" si="7">AL5/AJ5</f>
+        <v>9.9478731960483791E-2</v>
+      </c>
+      <c r="AN5" s="11">
+        <f t="shared" ref="AN5:AN18" si="8">D5+H5</f>
+        <v>1583000</v>
+      </c>
+      <c r="AO5" s="12">
+        <f t="shared" si="0"/>
+        <v>1060</v>
+      </c>
+      <c r="AP5" s="15">
+        <f t="shared" si="1"/>
+        <v>3287</v>
+      </c>
+      <c r="AQ5" s="14">
+        <f t="shared" ref="AQ5:AQ18" si="9">AP5/AN5</f>
+        <v>2.0764371446620341E-3</v>
+      </c>
+      <c r="AR5" s="11">
+        <f t="shared" ref="AR5:AR18" si="10">D5+H5+L5+P5+T5+X5+AB5</f>
+        <v>9046992</v>
+      </c>
+      <c r="AS5" s="12">
+        <f t="shared" si="2"/>
+        <v>611</v>
+      </c>
+      <c r="AT5" s="15">
+        <f t="shared" si="3"/>
+        <v>224206</v>
+      </c>
+      <c r="AU5" s="14">
+        <f t="shared" ref="AU5:AU18" si="11">AT5/AR5</f>
+        <v>2.4782380707311338E-2</v>
+      </c>
     </row>
-    <row r="6" spans="3:35" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:47" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
       <c r="C6" s="5">
         <v>45809</v>
       </c>
@@ -1043,8 +1234,59 @@
       <c r="AI6" s="14">
         <v>0.94510000000000005</v>
       </c>
+      <c r="AJ6" s="11">
+        <f t="shared" si="4"/>
+        <v>5462190</v>
+      </c>
+      <c r="AK6" s="12">
+        <f t="shared" si="5"/>
+        <v>7974</v>
+      </c>
+      <c r="AL6" s="15">
+        <f t="shared" si="6"/>
+        <v>-293949</v>
+      </c>
+      <c r="AM6" s="14">
+        <f t="shared" si="7"/>
+        <v>-5.381522795801684E-2</v>
+      </c>
+      <c r="AN6" s="11">
+        <f t="shared" si="8"/>
+        <v>1784800</v>
+      </c>
+      <c r="AO6" s="12">
+        <f t="shared" si="0"/>
+        <v>1236</v>
+      </c>
+      <c r="AP6" s="15">
+        <f t="shared" si="1"/>
+        <v>-322509</v>
+      </c>
+      <c r="AQ6" s="14">
+        <f t="shared" si="9"/>
+        <v>-0.18069755714926042</v>
+      </c>
+      <c r="AR6" s="11">
+        <f t="shared" si="10"/>
+        <v>9837684</v>
+      </c>
+      <c r="AS6" s="12">
+        <f t="shared" si="2"/>
+        <v>742</v>
+      </c>
+      <c r="AT6" s="15">
+        <f t="shared" si="3"/>
+        <v>463151</v>
+      </c>
+      <c r="AU6" s="14">
+        <f t="shared" si="11"/>
+        <v>4.7079271909933273E-2</v>
+      </c>
     </row>
-    <row r="7" spans="3:35" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:47" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
       <c r="C7" s="5">
         <v>45839</v>
       </c>
@@ -1136,8 +1378,59 @@
       <c r="AI7" s="14">
         <v>0.94469999999999998</v>
       </c>
+      <c r="AJ7" s="11">
+        <f t="shared" si="4"/>
+        <v>4997760</v>
+      </c>
+      <c r="AK7" s="12">
+        <f t="shared" si="5"/>
+        <v>7296</v>
+      </c>
+      <c r="AL7" s="15">
+        <f t="shared" si="6"/>
+        <v>-153874</v>
+      </c>
+      <c r="AM7" s="14">
+        <f t="shared" si="7"/>
+        <v>-3.0788593289793827E-2</v>
+      </c>
+      <c r="AN7" s="11">
+        <f t="shared" si="8"/>
+        <v>1695600</v>
+      </c>
+      <c r="AO7" s="12">
+        <f t="shared" si="0"/>
+        <v>1186</v>
+      </c>
+      <c r="AP7" s="15">
+        <f t="shared" si="1"/>
+        <v>-492008</v>
+      </c>
+      <c r="AQ7" s="14">
+        <f t="shared" si="9"/>
+        <v>-0.29016749233309741</v>
+      </c>
+      <c r="AR7" s="11">
+        <f t="shared" si="10"/>
+        <v>9476967</v>
+      </c>
+      <c r="AS7" s="12">
+        <f t="shared" si="2"/>
+        <v>801</v>
+      </c>
+      <c r="AT7" s="15">
+        <f t="shared" si="3"/>
+        <v>454218</v>
+      </c>
+      <c r="AU7" s="14">
+        <f t="shared" si="11"/>
+        <v>4.7928625265868288E-2</v>
+      </c>
     </row>
-    <row r="8" spans="3:35" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:47" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
       <c r="C8" s="5">
         <v>45870</v>
       </c>
@@ -1229,8 +1522,59 @@
       <c r="AI8" s="14">
         <v>0.86070000000000002</v>
       </c>
+      <c r="AJ8" s="11">
+        <f t="shared" si="4"/>
+        <v>5425885</v>
+      </c>
+      <c r="AK8" s="12">
+        <f t="shared" si="5"/>
+        <v>7921</v>
+      </c>
+      <c r="AL8" s="15">
+        <f t="shared" si="6"/>
+        <v>614383</v>
+      </c>
+      <c r="AM8" s="14">
+        <f t="shared" si="7"/>
+        <v>0.11323185065662099</v>
+      </c>
+      <c r="AN8" s="11">
+        <f t="shared" si="8"/>
+        <v>1966400</v>
+      </c>
+      <c r="AO8" s="12">
+        <f t="shared" si="0"/>
+        <v>1318</v>
+      </c>
+      <c r="AP8" s="15">
+        <f t="shared" si="1"/>
+        <v>543318</v>
+      </c>
+      <c r="AQ8" s="14">
+        <f t="shared" si="9"/>
+        <v>0.27630085435313262</v>
+      </c>
+      <c r="AR8" s="11">
+        <f t="shared" si="10"/>
+        <v>10454741</v>
+      </c>
+      <c r="AS8" s="12">
+        <f t="shared" si="2"/>
+        <v>858</v>
+      </c>
+      <c r="AT8" s="15">
+        <f t="shared" si="3"/>
+        <v>932436</v>
+      </c>
+      <c r="AU8" s="14">
+        <f t="shared" si="11"/>
+        <v>8.9187862233985518E-2</v>
+      </c>
     </row>
-    <row r="9" spans="3:35" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:47" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
       <c r="C9" s="5">
         <v>45901</v>
       </c>
@@ -1322,8 +1666,59 @@
       <c r="AI9" s="14">
         <v>0.72540000000000004</v>
       </c>
+      <c r="AJ9" s="11">
+        <f t="shared" si="4"/>
+        <v>5777975</v>
+      </c>
+      <c r="AK9" s="12">
+        <f t="shared" si="5"/>
+        <v>8435</v>
+      </c>
+      <c r="AL9" s="15">
+        <f t="shared" si="6"/>
+        <v>873217</v>
+      </c>
+      <c r="AM9" s="14">
+        <f t="shared" si="7"/>
+        <v>0.15112855282343729</v>
+      </c>
+      <c r="AN9" s="11">
+        <f t="shared" si="8"/>
+        <v>3078200</v>
+      </c>
+      <c r="AO9" s="12">
+        <f t="shared" si="0"/>
+        <v>2063</v>
+      </c>
+      <c r="AP9" s="15">
+        <f t="shared" si="1"/>
+        <v>1501492</v>
+      </c>
+      <c r="AQ9" s="14">
+        <f t="shared" si="9"/>
+        <v>0.48778247027483596</v>
+      </c>
+      <c r="AR9" s="11">
+        <f t="shared" si="10"/>
+        <v>12279361</v>
+      </c>
+      <c r="AS9" s="12">
+        <f t="shared" si="2"/>
+        <v>1133</v>
+      </c>
+      <c r="AT9" s="15">
+        <f t="shared" si="3"/>
+        <v>1747113</v>
+      </c>
+      <c r="AU9" s="14">
+        <f t="shared" si="11"/>
+        <v>0.14228044928396519</v>
+      </c>
     </row>
-    <row r="10" spans="3:35" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:47" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
       <c r="C10" s="5">
         <v>45931</v>
       </c>
@@ -1423,8 +1818,59 @@
       <c r="AI10" s="14">
         <v>0.84689999999999999</v>
       </c>
+      <c r="AJ10" s="11">
+        <f t="shared" si="4"/>
+        <v>13531490</v>
+      </c>
+      <c r="AK10" s="12">
+        <f t="shared" si="5"/>
+        <v>19754</v>
+      </c>
+      <c r="AL10" s="15">
+        <f t="shared" si="6"/>
+        <v>8549099</v>
+      </c>
+      <c r="AM10" s="14">
+        <f t="shared" si="7"/>
+        <v>0.63179287720716637</v>
+      </c>
+      <c r="AN10" s="11">
+        <f t="shared" si="8"/>
+        <v>6183960</v>
+      </c>
+      <c r="AO10" s="12">
+        <f t="shared" si="0"/>
+        <v>3980</v>
+      </c>
+      <c r="AP10" s="15">
+        <f t="shared" si="1"/>
+        <v>4454187</v>
+      </c>
+      <c r="AQ10" s="14">
+        <f t="shared" si="9"/>
+        <v>0.72028069392428151</v>
+      </c>
+      <c r="AR10" s="11">
+        <f t="shared" si="10"/>
+        <v>23980902</v>
+      </c>
+      <c r="AS10" s="12">
+        <f t="shared" si="2"/>
+        <v>1493</v>
+      </c>
+      <c r="AT10" s="15">
+        <f t="shared" si="3"/>
+        <v>2382069</v>
+      </c>
+      <c r="AU10" s="14">
+        <f t="shared" si="11"/>
+        <v>9.9331918374046146E-2</v>
+      </c>
     </row>
-    <row r="11" spans="3:35" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:47" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
       <c r="C11" s="5">
         <v>45962</v>
       </c>
@@ -1524,8 +1970,59 @@
       <c r="AI11" s="14">
         <v>0.88780000000000003</v>
       </c>
+      <c r="AJ11" s="11">
+        <f t="shared" si="4"/>
+        <v>6943845</v>
+      </c>
+      <c r="AK11" s="12">
+        <f t="shared" si="5"/>
+        <v>10137</v>
+      </c>
+      <c r="AL11" s="15">
+        <f t="shared" si="6"/>
+        <v>3014778</v>
+      </c>
+      <c r="AM11" s="14">
+        <f t="shared" si="7"/>
+        <v>0.43416550916675128</v>
+      </c>
+      <c r="AN11" s="11">
+        <f t="shared" si="8"/>
+        <v>2528000</v>
+      </c>
+      <c r="AO11" s="12">
+        <f t="shared" si="0"/>
+        <v>1665</v>
+      </c>
+      <c r="AP11" s="15">
+        <f t="shared" si="1"/>
+        <v>1284478</v>
+      </c>
+      <c r="AQ11" s="14">
+        <f t="shared" si="9"/>
+        <v>0.50810047468354436</v>
+      </c>
+      <c r="AR11" s="11">
+        <f t="shared" si="10"/>
+        <v>12224714</v>
+      </c>
+      <c r="AS11" s="12">
+        <f t="shared" si="2"/>
+        <v>925</v>
+      </c>
+      <c r="AT11" s="15">
+        <f t="shared" si="3"/>
+        <v>1020457</v>
+      </c>
+      <c r="AU11" s="14">
+        <f t="shared" si="11"/>
+        <v>8.3474918104423548E-2</v>
+      </c>
     </row>
-    <row r="12" spans="3:35" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:47" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
       <c r="C12" s="5">
         <v>45992</v>
       </c>
@@ -1625,8 +2122,59 @@
       <c r="AI12" s="14">
         <v>0.85599999999999998</v>
       </c>
+      <c r="AJ12" s="11">
+        <f t="shared" si="4"/>
+        <v>4232615</v>
+      </c>
+      <c r="AK12" s="12">
+        <f t="shared" si="5"/>
+        <v>6179</v>
+      </c>
+      <c r="AL12" s="15">
+        <f t="shared" si="6"/>
+        <v>78190</v>
+      </c>
+      <c r="AM12" s="14">
+        <f t="shared" si="7"/>
+        <v>1.8473213368095136E-2</v>
+      </c>
+      <c r="AN12" s="11">
+        <f t="shared" si="8"/>
+        <v>2156600</v>
+      </c>
+      <c r="AO12" s="12">
+        <f t="shared" si="0"/>
+        <v>1449</v>
+      </c>
+      <c r="AP12" s="15">
+        <f t="shared" si="1"/>
+        <v>455011</v>
+      </c>
+      <c r="AQ12" s="14">
+        <f t="shared" si="9"/>
+        <v>0.21098534730594454</v>
+      </c>
+      <c r="AR12" s="11">
+        <f t="shared" si="10"/>
+        <v>9225091</v>
+      </c>
+      <c r="AS12" s="12">
+        <f t="shared" si="2"/>
+        <v>934</v>
+      </c>
+      <c r="AT12" s="15">
+        <f t="shared" si="3"/>
+        <v>987518</v>
+      </c>
+      <c r="AU12" s="14">
+        <f t="shared" si="11"/>
+        <v>0.10704696571556856</v>
+      </c>
     </row>
-    <row r="13" spans="3:35" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:47" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
       <c r="C13" s="5">
         <v>46023</v>
       </c>
@@ -1726,8 +2274,59 @@
       <c r="AI13" s="14">
         <v>0.87539999999999996</v>
       </c>
+      <c r="AJ13" s="11">
+        <f t="shared" si="4"/>
+        <v>4707320</v>
+      </c>
+      <c r="AK13" s="12">
+        <f t="shared" si="5"/>
+        <v>6872</v>
+      </c>
+      <c r="AL13" s="15">
+        <f t="shared" si="6"/>
+        <v>549481</v>
+      </c>
+      <c r="AM13" s="14">
+        <f t="shared" si="7"/>
+        <v>0.11672905177468283</v>
+      </c>
+      <c r="AN13" s="11">
+        <f t="shared" si="8"/>
+        <v>3934200</v>
+      </c>
+      <c r="AO13" s="12">
+        <f t="shared" si="0"/>
+        <v>2569</v>
+      </c>
+      <c r="AP13" s="15">
+        <f t="shared" si="1"/>
+        <v>2135448</v>
+      </c>
+      <c r="AQ13" s="14">
+        <f t="shared" si="9"/>
+        <v>0.5427909104773524</v>
+      </c>
+      <c r="AR13" s="11">
+        <f t="shared" si="10"/>
+        <v>11682843</v>
+      </c>
+      <c r="AS13" s="12">
+        <f t="shared" si="2"/>
+        <v>1178</v>
+      </c>
+      <c r="AT13" s="15">
+        <f t="shared" si="3"/>
+        <v>1012417</v>
+      </c>
+      <c r="AU13" s="14">
+        <f t="shared" si="11"/>
+        <v>8.6658444352971278E-2</v>
+      </c>
     </row>
-    <row r="14" spans="3:35" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:47" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
       <c r="C14" s="5">
         <v>46054</v>
       </c>
@@ -1827,8 +2426,59 @@
       <c r="AI14" s="14">
         <v>0.78029999999999999</v>
       </c>
+      <c r="AJ14" s="11">
+        <f t="shared" si="4"/>
+        <v>5051190</v>
+      </c>
+      <c r="AK14" s="12">
+        <f t="shared" si="5"/>
+        <v>7374</v>
+      </c>
+      <c r="AL14" s="15">
+        <f t="shared" si="6"/>
+        <v>227883</v>
+      </c>
+      <c r="AM14" s="14">
+        <f t="shared" si="7"/>
+        <v>4.511471554227816E-2</v>
+      </c>
+      <c r="AN14" s="11">
+        <f t="shared" si="8"/>
+        <v>2976200</v>
+      </c>
+      <c r="AO14" s="12">
+        <f t="shared" si="0"/>
+        <v>1931</v>
+      </c>
+      <c r="AP14" s="15">
+        <f t="shared" si="1"/>
+        <v>1577972</v>
+      </c>
+      <c r="AQ14" s="14">
+        <f t="shared" si="9"/>
+        <v>0.53019689536993486</v>
+      </c>
+      <c r="AR14" s="11">
+        <f t="shared" si="10"/>
+        <v>10994977</v>
+      </c>
+      <c r="AS14" s="12">
+        <f t="shared" si="2"/>
+        <v>1195</v>
+      </c>
+      <c r="AT14" s="15">
+        <f t="shared" si="3"/>
+        <v>1228261</v>
+      </c>
+      <c r="AU14" s="14">
+        <f t="shared" si="11"/>
+        <v>0.111711102260605</v>
+      </c>
     </row>
-    <row r="15" spans="3:35" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:47" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
       <c r="C15" s="5">
         <v>46082</v>
       </c>
@@ -1928,8 +2578,59 @@
       <c r="AI15" s="14">
         <v>0.33079999999999998</v>
       </c>
+      <c r="AJ15" s="11">
+        <f t="shared" si="4"/>
+        <v>5172435</v>
+      </c>
+      <c r="AK15" s="12">
+        <f t="shared" si="5"/>
+        <v>7551</v>
+      </c>
+      <c r="AL15" s="15">
+        <f t="shared" si="6"/>
+        <v>1068391</v>
+      </c>
+      <c r="AM15" s="14">
+        <f t="shared" si="7"/>
+        <v>0.20655474645887284</v>
+      </c>
+      <c r="AN15" s="11">
+        <f t="shared" si="8"/>
+        <v>3999003</v>
+      </c>
+      <c r="AO15" s="12">
+        <f t="shared" si="0"/>
+        <v>2436</v>
+      </c>
+      <c r="AP15" s="15">
+        <f t="shared" si="1"/>
+        <v>2090854</v>
+      </c>
+      <c r="AQ15" s="14">
+        <f t="shared" si="9"/>
+        <v>0.52284381882184139</v>
+      </c>
+      <c r="AR15" s="11">
+        <f t="shared" si="10"/>
+        <v>14720283</v>
+      </c>
+      <c r="AS15" s="12">
+        <f t="shared" si="2"/>
+        <v>2520</v>
+      </c>
+      <c r="AT15" s="15">
+        <f t="shared" si="3"/>
+        <v>3830180</v>
+      </c>
+      <c r="AU15" s="14">
+        <f t="shared" si="11"/>
+        <v>0.26019744321491645</v>
+      </c>
     </row>
-    <row r="16" spans="3:35" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:47" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>18</v>
+      </c>
       <c r="C16" s="5">
         <v>46113</v>
       </c>
@@ -1982,16 +2683,16 @@
         <v>-1.0358605872523274</v>
       </c>
       <c r="T16" s="11">
-        <v>5642345</v>
+        <v>5971825</v>
       </c>
       <c r="U16" s="12">
         <v>8237</v>
       </c>
       <c r="V16" s="13">
-        <v>1042193</v>
+        <v>1371673</v>
       </c>
       <c r="W16" s="14">
-        <v>0.18470919449271536</v>
+        <v>0.22969999999999999</v>
       </c>
       <c r="X16" s="11">
         <v>77992</v>
@@ -2018,7 +2719,8 @@
         <v>0.29151552072660813</v>
       </c>
       <c r="AF16" s="11">
-        <v>826795</v>
+        <f>AG16*725</f>
+        <v>875075</v>
       </c>
       <c r="AG16" s="12">
         <v>1207</v>
@@ -2029,8 +2731,59 @@
       <c r="AI16" s="14">
         <v>0.64990000000000003</v>
       </c>
+      <c r="AJ16" s="11">
+        <f t="shared" si="4"/>
+        <v>5096750</v>
+      </c>
+      <c r="AK16" s="12">
+        <f t="shared" si="5"/>
+        <v>7030</v>
+      </c>
+      <c r="AL16" s="15">
+        <f t="shared" si="6"/>
+        <v>834299</v>
+      </c>
+      <c r="AM16" s="14">
+        <f t="shared" si="7"/>
+        <v>0.16369235297002993</v>
+      </c>
+      <c r="AN16" s="11">
+        <f t="shared" si="8"/>
+        <v>2867000</v>
+      </c>
+      <c r="AO16" s="12">
+        <f t="shared" si="0"/>
+        <v>1776</v>
+      </c>
+      <c r="AP16" s="15">
+        <f t="shared" si="1"/>
+        <v>1174415</v>
+      </c>
+      <c r="AQ16" s="14">
+        <f t="shared" si="9"/>
+        <v>0.40963201953261247</v>
+      </c>
+      <c r="AR16" s="11">
+        <f t="shared" si="10"/>
+        <v>11808224</v>
+      </c>
+      <c r="AS16" s="12">
+        <f t="shared" si="2"/>
+        <v>1515</v>
+      </c>
+      <c r="AT16" s="15">
+        <f t="shared" si="3"/>
+        <v>2367976</v>
+      </c>
+      <c r="AU16" s="14">
+        <f t="shared" si="11"/>
+        <v>0.20053616869056684</v>
+      </c>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:47" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
       <c r="C17" s="5">
         <v>46143</v>
       </c>
@@ -2083,16 +2836,16 @@
         <v>-0.4814613570318852</v>
       </c>
       <c r="T17" s="11">
-        <v>5675225</v>
+        <v>6006625</v>
       </c>
       <c r="U17" s="12">
         <v>8285</v>
       </c>
       <c r="V17" s="13">
-        <v>534776</v>
+        <v>866176</v>
       </c>
       <c r="W17" s="14">
-        <v>9.4229920399631739E-2</v>
+        <v>0.14419999999999999</v>
       </c>
       <c r="X17" s="11">
         <v>45295</v>
@@ -2119,7 +2872,8 @@
         <v>0.26190668715128973</v>
       </c>
       <c r="AF17" s="11">
-        <v>828165</v>
+        <f t="shared" ref="AF17:AF18" si="12">AG17*725</f>
+        <v>876525</v>
       </c>
       <c r="AG17" s="12">
         <v>1209</v>
@@ -2130,8 +2884,59 @@
       <c r="AI17" s="14">
         <v>0.34710000000000002</v>
       </c>
+      <c r="AJ17" s="11">
+        <f t="shared" si="4"/>
+        <v>5130100</v>
+      </c>
+      <c r="AK17" s="12">
+        <f t="shared" si="5"/>
+        <v>7076</v>
+      </c>
+      <c r="AL17" s="13">
+        <f t="shared" si="6"/>
+        <v>578702</v>
+      </c>
+      <c r="AM17" s="14">
+        <f t="shared" si="7"/>
+        <v>0.11280520847546831</v>
+      </c>
+      <c r="AN17" s="11">
+        <f t="shared" si="8"/>
+        <v>2508000</v>
+      </c>
+      <c r="AO17" s="12">
+        <f t="shared" si="0"/>
+        <v>1494</v>
+      </c>
+      <c r="AP17" s="13">
+        <f t="shared" si="1"/>
+        <v>479890</v>
+      </c>
+      <c r="AQ17" s="14">
+        <f t="shared" si="9"/>
+        <v>0.19134370015948962</v>
+      </c>
+      <c r="AR17" s="11">
+        <f t="shared" si="10"/>
+        <v>11818380</v>
+      </c>
+      <c r="AS17" s="12">
+        <f t="shared" si="2"/>
+        <v>1704</v>
+      </c>
+      <c r="AT17" s="13">
+        <f t="shared" si="3"/>
+        <v>2116826</v>
+      </c>
+      <c r="AU17" s="14">
+        <f t="shared" si="11"/>
+        <v>0.17911304256590158</v>
+      </c>
     </row>
-    <row r="18" spans="3:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:47" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B18" t="s">
+        <v>18</v>
+      </c>
       <c r="C18" s="16">
         <v>46174</v>
       </c>
@@ -2184,16 +2989,16 @@
         <v>-0.84158384346993909</v>
       </c>
       <c r="T18" s="17">
-        <v>6502705</v>
+        <v>6882425</v>
       </c>
       <c r="U18" s="18">
         <v>9493</v>
       </c>
       <c r="V18" s="19">
-        <v>1711901</v>
+        <v>2091621</v>
       </c>
       <c r="W18" s="20">
-        <v>0.26325982802541403</v>
+        <v>0.3039</v>
       </c>
       <c r="X18" s="17">
         <v>106040</v>
@@ -2220,7 +3025,8 @@
         <v>0.46378911174785098</v>
       </c>
       <c r="AF18" s="17">
-        <v>1113125</v>
+        <f t="shared" si="12"/>
+        <v>1178125</v>
       </c>
       <c r="AG18" s="18">
         <v>1625</v>
@@ -2231,17 +3037,68 @@
       <c r="AI18" s="20">
         <v>0.88890000000000002</v>
       </c>
+      <c r="AJ18" s="17">
+        <f t="shared" si="4"/>
+        <v>5704300</v>
+      </c>
+      <c r="AK18" s="18">
+        <f t="shared" si="5"/>
+        <v>7868</v>
+      </c>
+      <c r="AL18" s="19">
+        <f t="shared" si="6"/>
+        <v>1102207</v>
+      </c>
+      <c r="AM18" s="20">
+        <f t="shared" si="7"/>
+        <v>0.19322388373683011</v>
+      </c>
+      <c r="AN18" s="17">
+        <f t="shared" si="8"/>
+        <v>2581000</v>
+      </c>
+      <c r="AO18" s="18">
+        <f t="shared" si="0"/>
+        <v>1570</v>
+      </c>
+      <c r="AP18" s="19">
+        <f t="shared" si="1"/>
+        <v>220248</v>
+      </c>
+      <c r="AQ18" s="20">
+        <f t="shared" si="9"/>
+        <v>8.533436652460287E-2</v>
+      </c>
+      <c r="AR18" s="17">
+        <f t="shared" si="10"/>
+        <v>12899018</v>
+      </c>
+      <c r="AS18" s="18">
+        <f t="shared" si="2"/>
+        <v>1681</v>
+      </c>
+      <c r="AT18" s="19">
+        <f t="shared" si="3"/>
+        <v>2892983</v>
+      </c>
+      <c r="AU18" s="20">
+        <f t="shared" si="11"/>
+        <v>0.22427932110800994</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="AB2:AE2"/>
-    <mergeCell ref="AF2:AI2"/>
+  <mergeCells count="11">
+    <mergeCell ref="X2:AA2"/>
     <mergeCell ref="D2:G2"/>
     <mergeCell ref="H2:K2"/>
     <mergeCell ref="L2:O2"/>
     <mergeCell ref="P2:S2"/>
     <mergeCell ref="T2:W2"/>
-    <mergeCell ref="X2:AA2"/>
+    <mergeCell ref="AJ2:AM2"/>
+    <mergeCell ref="AN2:AQ2"/>
+    <mergeCell ref="AR2:AU2"/>
+    <mergeCell ref="AB2:AE2"/>
+    <mergeCell ref="AF2:AI2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
